--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N77_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N77_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>77.17821329119252</v>
+        <v>12.54145965981878</v>
       </c>
       <c r="D2" t="n">
-        <v>19.8201118445583</v>
+        <v>3.220768174740724</v>
       </c>
       <c r="E2" t="n">
-        <v>11.26307067923773</v>
+        <v>1.830248985376131</v>
       </c>
       <c r="F2" t="n">
-        <v>17.61222927780869</v>
+        <v>2.861987257643912</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>64.50789859663251</v>
+        <v>10.48253352195278</v>
       </c>
       <c r="D3" t="n">
-        <v>22.63624250054355</v>
+        <v>3.678389406338327</v>
       </c>
       <c r="E3" t="n">
-        <v>11.26307067923773</v>
+        <v>1.830248985376131</v>
       </c>
       <c r="F3" t="n">
-        <v>17.61222927780869</v>
+        <v>2.861987257643912</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>55.56195074432349</v>
+        <v>9.028816995952567</v>
       </c>
       <c r="D4" t="n">
-        <v>17.0173052172733</v>
+        <v>2.765312097806911</v>
       </c>
       <c r="E4" t="n">
-        <v>11.26307067923773</v>
+        <v>1.830248985376131</v>
       </c>
       <c r="F4" t="n">
-        <v>17.61222927780869</v>
+        <v>2.861987257643912</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>60.42256566675053</v>
+        <v>9.818666920846962</v>
       </c>
       <c r="D5" t="n">
-        <v>57.50946276599822</v>
+        <v>9.345287699474712</v>
       </c>
       <c r="E5" t="n">
-        <v>11.26307067923773</v>
+        <v>1.830248985376131</v>
       </c>
       <c r="F5" t="n">
-        <v>17.61222927780869</v>
+        <v>2.861987257643912</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>36.41636277769408</v>
+        <v>5.917658951375287</v>
       </c>
       <c r="D6" t="n">
-        <v>33.73956793940047</v>
+        <v>5.482679790152577</v>
       </c>
       <c r="E6" t="n">
-        <v>11.26307067923773</v>
+        <v>1.830248985376131</v>
       </c>
       <c r="F6" t="n">
-        <v>17.61222927780869</v>
+        <v>2.861987257643912</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>51.61171814641988</v>
+        <v>8.386904198793232</v>
       </c>
       <c r="D7" t="n">
-        <v>46.64446195636124</v>
+        <v>7.579725067908702</v>
       </c>
       <c r="E7" t="n">
-        <v>11.26307067923773</v>
+        <v>1.830248985376131</v>
       </c>
       <c r="F7" t="n">
-        <v>17.61222927780869</v>
+        <v>2.861987257643912</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>60.88230326710763</v>
+        <v>9.89337428090499</v>
       </c>
       <c r="D8" t="n">
-        <v>57.77813371597638</v>
+        <v>9.388946728846163</v>
       </c>
       <c r="E8" t="n">
-        <v>11.26307067923773</v>
+        <v>1.830248985376131</v>
       </c>
       <c r="F8" t="n">
-        <v>17.61222927780869</v>
+        <v>2.861987257643912</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>62.6214926909645</v>
+        <v>10.17599256228173</v>
       </c>
       <c r="D9" t="n">
-        <v>55.00238868737576</v>
+        <v>8.937888161698561</v>
       </c>
       <c r="E9" t="n">
-        <v>11.26307067923773</v>
+        <v>1.830248985376131</v>
       </c>
       <c r="F9" t="n">
-        <v>17.61222927780869</v>
+        <v>2.861987257643912</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>73.14667752163857</v>
+        <v>11.88633509726627</v>
       </c>
       <c r="D10" t="n">
-        <v>65.51434739469809</v>
+        <v>10.64608145163844</v>
       </c>
       <c r="E10" t="n">
-        <v>11.26307067923773</v>
+        <v>1.830248985376131</v>
       </c>
       <c r="F10" t="n">
-        <v>17.61222927780869</v>
+        <v>2.861987257643912</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
